--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,23 +869,23 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>125</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G16" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.294117647058</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K16" s="15">
-        <v>-27.272727272727</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="M16" s="15">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.250996015936</v>
+        <v>-85.211267605633</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>12</v>
+      </c>
+      <c r="D17" s="14">
         <v>10</v>
       </c>
-      <c r="D17" s="14">
-        <v>11</v>
-      </c>
       <c r="E17" s="15">
-        <v>-9.090909090909</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G17" s="14">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.611111111111</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J17" s="14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>-24</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L17" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="M17" s="15">
-        <v>49.019607843137</v>
+        <v>47.540983606557</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.593220338983</v>
+        <v>-33.823529411764</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-3.703703703703</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.333333333333</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.095238095238</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.114068441064</v>
+        <v>-90.202702702702</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-37.5</v>
+        <v>142.857142857143</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G19" s="14">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H19" s="15">
-        <v>-44.285714285714</v>
+        <v>-34.375</v>
       </c>
       <c r="I19" s="14">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="J19" s="14">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>-38.043478260869</v>
+        <v>-25.252525252525</v>
       </c>
       <c r="L19" s="15">
-        <v>-43.564356435643</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="M19" s="15">
-        <v>46.153846153846</v>
+        <v>64.444444444444</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.307692307692</v>
+        <v>-10.843373493975</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-56.521739130434</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K20" s="15">
-        <v>-35.714285714285</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.935483870967</v>
+        <v>-53.658536585365</v>
       </c>
       <c r="M20" s="15">
-        <v>50</v>
+        <v>35.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.526315789473</v>
+        <v>-91.363636363636</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.128205128205</v>
+        <v>31.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G21" s="17">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="H21" s="18">
-        <v>-31.555555555555</v>
+        <v>-28.095238095238</v>
       </c>
       <c r="I21" s="17">
-        <v>218</v>
+        <v>265</v>
       </c>
       <c r="J21" s="17">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.599326599326</v>
+        <v>-20.180722891566</v>
       </c>
       <c r="L21" s="18">
-        <v>-33.128834355828</v>
+        <v>-30.989583333333</v>
       </c>
       <c r="M21" s="18">
-        <v>14.736842105263</v>
+        <v>20.454545454545</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.696767001114</v>
+        <v>-74.246841593780</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,25 +1192,25 @@
         <v>3</v>
       </c>
       <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-40</v>
+      </c>
+      <c r="I22" s="14">
         <v>6</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-50</v>
-      </c>
-      <c r="I22" s="14">
-        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>-28.571428571428</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" s="15">
-        <v>-28.571428571428</v>
+        <v>-12.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.571428571428</v>
+        <v>-12.5</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.75</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H24" s="15">
-        <v>-35.074626865671</v>
+        <v>-35.114503816793</v>
       </c>
       <c r="I24" s="14">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="J24" s="14">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="K24" s="15">
-        <v>-36.170212765957</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-40</v>
+        <v>-39.240506329113</v>
       </c>
       <c r="M24" s="15">
-        <v>-21.052631578947</v>
+        <v>-16.763005780346</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-56.25</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H25" s="15">
-        <v>-59.090909090909</v>
+        <v>-51.111111111111</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="K25" s="15">
-        <v>-53.030303030303</v>
+        <v>-50.649350649350</v>
       </c>
       <c r="L25" s="15">
-        <v>-71.818181818181</v>
+        <v>-70.992366412213</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>17.647058823529</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.204819277108</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="I26" s="14">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="J26" s="14">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="K26" s="15">
-        <v>5.309734513274</v>
+        <v>-3.649635036496</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.768115942029</v>
+        <v>-17.5</v>
       </c>
       <c r="M26" s="15">
-        <v>17.821782178217</v>
+        <v>11.864406779661</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
         <v>3</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>80</v>
+        <v>-12.5</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>27</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>76.470588235294</v>
+        <v>61.904761904761</v>
       </c>
       <c r="L28" s="15">
-        <v>130.769230769231</v>
+        <v>161.538461538462</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,28 +1476,28 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
         <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L29" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N29" s="15">
         <v>-50</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-20</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M30" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,39 +885,39 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>6</v>
-      </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
         <v>42.857142857142</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>22.222222222222</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F16" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.684210526315</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="I16" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.754716981132</v>
+        <v>-15</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.235294117647</v>
+        <v>-32</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.5</v>
+        <v>-13.559322033898</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.211267605633</v>
+        <v>-83.911671924290</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F17" s="14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G17" s="14">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" s="15">
-        <v>-20</v>
+        <v>-22.033898305084</v>
       </c>
       <c r="I17" s="14">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J17" s="14">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.181818181818</v>
+        <v>-14.049586776859</v>
       </c>
       <c r="L17" s="15">
-        <v>-25</v>
+        <v>-25.179856115107</v>
       </c>
       <c r="M17" s="15">
-        <v>47.540983606557</v>
+        <v>44.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>-33.823529411764</v>
+        <v>-35.403726708074</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.047619047619</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>-3.333333333333</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.705882352941</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="M18" s="15">
-        <v>-34.090909090909</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.202702702702</v>
+        <v>-89.361702127659</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>142.857142857143</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H19" s="15">
-        <v>-34.375</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J19" s="14">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.252525252525</v>
+        <v>-25.217391304347</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.928571428571</v>
+        <v>-27.731092436974</v>
       </c>
       <c r="M19" s="15">
-        <v>64.444444444444</v>
+        <v>72</v>
       </c>
       <c r="N19" s="15">
-        <v>-10.843373493975</v>
+        <v>-11.340206185567</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
+        <v>26</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-57.692307692307</v>
+      </c>
+      <c r="I20" s="14">
         <v>24</v>
       </c>
-      <c r="H20" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I20" s="14">
-        <v>19</v>
-      </c>
       <c r="J20" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K20" s="15">
-        <v>-42.424242424242</v>
+        <v>-40</v>
       </c>
       <c r="L20" s="15">
-        <v>-53.658536585365</v>
+        <v>-44.186046511627</v>
       </c>
       <c r="M20" s="15">
-        <v>35.714285714285</v>
+        <v>50</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.363636363636</v>
+        <v>-90.204081632653</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>31.428571428571</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G21" s="17">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.095238095238</v>
+        <v>-22</v>
       </c>
       <c r="I21" s="17">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="J21" s="17">
-        <v>332</v>
+        <v>381</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.180722891566</v>
+        <v>-18.372703412073</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.989583333333</v>
+        <v>-26.650943396226</v>
       </c>
       <c r="M21" s="18">
-        <v>20.454545454545</v>
+        <v>22.924901185770</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.246841593780</v>
+        <v>-73.235800344234</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
@@ -1207,10 +1207,10 @@
         <v>-14.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>-60</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
         <v>8</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M23" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H24" s="15">
-        <v>-35.114503816793</v>
+        <v>-23.015873015873</v>
       </c>
       <c r="I24" s="14">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="J24" s="14">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.333333333333</v>
+        <v>-29.218106995884</v>
       </c>
       <c r="L24" s="15">
-        <v>-39.240506329113</v>
+        <v>-36.296296296296</v>
       </c>
       <c r="M24" s="15">
-        <v>-16.763005780346</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.363636363636</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>-51.111111111111</v>
+        <v>-48</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J25" s="14">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.649350649350</v>
+        <v>-47.191011235955</v>
       </c>
       <c r="L25" s="15">
-        <v>-70.992366412213</v>
+        <v>-68.456375838926</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E26" s="15">
-        <v>-29.166666666666</v>
+        <v>20.689655172413</v>
       </c>
       <c r="F26" s="14">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="G26" s="14">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.049382716049</v>
+        <v>3.488372093023</v>
       </c>
       <c r="I26" s="14">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="J26" s="14">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.649635036496</v>
+        <v>0.602409638554</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.5</v>
+        <v>-8.241758241758</v>
       </c>
       <c r="M26" s="15">
-        <v>11.864406779661</v>
+        <v>26.515151515151</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-66.666666666666</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>61.904761904761</v>
+        <v>63.636363636363</v>
       </c>
       <c r="L28" s="15">
-        <v>161.538461538462</v>
+        <v>157.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L29" s="15">
         <v>-50</v>
@@ -1500,39 +1500,39 @@
         <v>40</v>
       </c>
       <c r="N29" s="15">
-        <v>-50</v>
+        <v>-63.157894736842</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L30" s="15">
         <v>-28.571428571428</v>
@@ -1541,7 +1541,7 @@
         <v>25</v>
       </c>
       <c r="N30" s="15">
-        <v>-64.285714285714</v>
+        <v>-73.684210526315</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,63 +870,63 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-87.5</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
+        <v>11</v>
+      </c>
+      <c r="J15" s="14">
+        <v>6</v>
+      </c>
+      <c r="K15" s="15">
+        <v>83.333333333333</v>
+      </c>
+      <c r="L15" s="15">
+        <v>57.142857142857</v>
+      </c>
+      <c r="M15" s="15">
+        <v>83.333333333333</v>
+      </c>
+      <c r="N15" s="15">
         <v>10</v>
-      </c>
-      <c r="J15" s="14">
-        <v>5</v>
-      </c>
-      <c r="K15" s="15">
-        <v>100</v>
-      </c>
-      <c r="L15" s="15">
-        <v>42.857142857142</v>
-      </c>
-      <c r="M15" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="N15" s="15">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>14.285714285714</v>
+        <v>125</v>
       </c>
       <c r="F16" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G16" s="14">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>-10.810810810810</v>
+        <v>42.307692307692</v>
       </c>
       <c r="I16" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J16" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-15</v>
+        <v>-6.25</v>
       </c>
       <c r="L16" s="15">
-        <v>-32</v>
+        <v>-32.584269662921</v>
       </c>
       <c r="M16" s="15">
-        <v>-13.559322033898</v>
+        <v>-6.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.911671924290</v>
+        <v>-83.379501385041</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>9.090909090909</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G17" s="14">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.033898305084</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I17" s="14">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="J17" s="14">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.049586776859</v>
+        <v>-9.923664122137</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.179856115107</v>
+        <v>-29.341317365269</v>
       </c>
       <c r="M17" s="15">
-        <v>44.444444444444</v>
+        <v>43.902439024390</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.403726708074</v>
+        <v>-35.869565217391</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>6</v>
       </c>
-      <c r="D18" s="14">
-        <v>7</v>
-      </c>
       <c r="E18" s="15">
-        <v>-14.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.405405405405</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.256410256410</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.083333333333</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.361702127659</v>
+        <v>-89.784946236559</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14">
         <v>12</v>
       </c>
-      <c r="D19" s="14">
-        <v>16</v>
-      </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.666666666666</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="I19" s="14">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J19" s="14">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.217391304347</v>
+        <v>-29.133858267716</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.731092436974</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>72</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N19" s="15">
-        <v>-11.340206185567</v>
+        <v>-13.461538461538</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-28.571428571428</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-57.692307692307</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>-40</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="L20" s="15">
-        <v>-44.186046511627</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="M20" s="15">
-        <v>50</v>
+        <v>47.368421052631</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.204081632653</v>
+        <v>-90.070921985815</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.416666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G21" s="17">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="H21" s="18">
-        <v>-22</v>
+        <v>1.851851851851</v>
       </c>
       <c r="I21" s="17">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="J21" s="17">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.372703412073</v>
+        <v>-17.577197149643</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.650943396226</v>
+        <v>-28.747433264887</v>
       </c>
       <c r="M21" s="18">
-        <v>22.924901185770</v>
+        <v>24.372759856630</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.235800344234</v>
+        <v>-73.791540785498</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-25</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
@@ -1207,7 +1207,7 @@
         <v>-14.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>-64.705882352941</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>50</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-27.272727272727</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M23" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.015873015873</v>
+        <v>-24.576271186440</v>
       </c>
       <c r="I24" s="14">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="J24" s="14">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="K24" s="15">
-        <v>-29.218106995884</v>
+        <v>-32.116788321167</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.296296296296</v>
+        <v>-40</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.416666666666</v>
+        <v>-8.374384236453</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
         <v>7</v>
       </c>
-      <c r="D25" s="14">
-        <v>12</v>
-      </c>
       <c r="E25" s="15">
-        <v>-41.666666666666</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-48</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
         <v>47</v>
       </c>
       <c r="J25" s="14">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.191011235955</v>
+        <v>-51.041666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-68.456375838926</v>
+        <v>-72.352941176470</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>20.689655172413</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="14">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H26" s="15">
-        <v>3.488372093023</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="I26" s="14">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="J26" s="14">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="K26" s="15">
-        <v>0.602409638554</v>
+        <v>-0.531914893617</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.241758241758</v>
+        <v>-7.881773399014</v>
       </c>
       <c r="M26" s="15">
-        <v>26.515151515151</v>
+        <v>24.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
@@ -1403,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
@@ -1435,25 +1435,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="I28" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K28" s="15">
-        <v>63.636363636363</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>157.142857142857</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-63.157894736842</v>
+        <v>-76.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1538,10 +1538,10 @@
         <v>-28.571428571428</v>
       </c>
       <c r="M30" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-73.684210526315</v>
+        <v>-80.769230769230</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -879,10 +879,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L14" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M14" s="15">
         <v>-33.333333333333</v>
-      </c>
-      <c r="M14" s="15">
-        <v>0</v>
       </c>
       <c r="N14" s="15">
         <v>-81.818181818181</v>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>4</v>
       </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>83.333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="L15" s="15">
         <v>57.142857142857</v>
@@ -926,7 +926,7 @@
         <v>83.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>10</v>
+        <v>-15.384615384615</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>125</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>42.307692307692</v>
+        <v>40.740740740740</v>
       </c>
       <c r="I16" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.25</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.584269662921</v>
+        <v>-27.368421052631</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.25</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.379501385041</v>
+        <v>-82.575757575757</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>19.047619047619</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I17" s="14">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J17" s="14">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.923664122137</v>
+        <v>-9.933774834437</v>
       </c>
       <c r="L17" s="15">
-        <v>-29.341317365269</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M17" s="15">
-        <v>43.902439024390</v>
+        <v>46.236559139784</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.869565217391</v>
+        <v>-34.299516908212</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.052631578947</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.627906976744</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.627906976744</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-25.490196078431</v>
+        <v>-20.370370370370</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.784946236559</v>
+        <v>-89.276807980049</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E19" s="15">
-        <v>-58.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.686274509803</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="I19" s="14">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="K19" s="15">
-        <v>-29.133858267716</v>
+        <v>-29.139072847682</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.065359477124</v>
       </c>
       <c r="M19" s="15">
-        <v>63.636363636363</v>
+        <v>75.409836065573</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.461538461538</v>
+        <v>-10.833333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>-36.363636363636</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K20" s="15">
-        <v>-40.425531914893</v>
+        <v>-45.762711864406</v>
       </c>
       <c r="L20" s="15">
-        <v>-34.883720930232</v>
+        <v>-31.914893617021</v>
       </c>
       <c r="M20" s="15">
-        <v>47.368421052631</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.070921985815</v>
+        <v>-89.644012944983</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>-22.388059701492</v>
       </c>
       <c r="F21" s="17">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="G21" s="17">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="H21" s="18">
-        <v>1.851851851851</v>
+        <v>-5.789473684210</v>
       </c>
       <c r="I21" s="17">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="J21" s="17">
-        <v>421</v>
+        <v>488</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.577197149643</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.747433264887</v>
+        <v>-25.650557620817</v>
       </c>
       <c r="M21" s="18">
-        <v>24.372759856630</v>
+        <v>27.795527156549</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.791540785498</v>
+        <v>-72.546328071379</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,32 +1182,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="M22" s="15">
         <v>50</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>-30.769230769230</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>-64.516129032258</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F24" s="14">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.576271186440</v>
+        <v>-27.34375</v>
       </c>
       <c r="I24" s="14">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="J24" s="14">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.116788321167</v>
+        <v>-31.329113924050</v>
       </c>
       <c r="L24" s="15">
-        <v>-40</v>
+        <v>-37.822349570200</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.374384236453</v>
+        <v>-3.555555555555</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-85.714285714285</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-51.020408163265</v>
       </c>
       <c r="I25" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="K25" s="15">
-        <v>-51.041666666666</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="L25" s="15">
-        <v>-72.352941176470</v>
+        <v>-70.430107526881</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="F26" s="14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G26" s="14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.173913043478</v>
+        <v>-13.265306122449</v>
       </c>
       <c r="I26" s="14">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="J26" s="14">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.531914893617</v>
+        <v>-5.213270142180</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.881773399014</v>
+        <v>-13.419913419913</v>
       </c>
       <c r="M26" s="15">
-        <v>24.666666666666</v>
+        <v>16.959064327485</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1429,31 +1429,31 @@
         <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
+        <v>10</v>
+      </c>
+      <c r="G28" s="14">
+        <v>11</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="I28" s="14">
+        <v>41</v>
+      </c>
+      <c r="J28" s="14">
         <v>27</v>
       </c>
-      <c r="G28" s="14">
-        <v>10</v>
-      </c>
-      <c r="H28" s="15">
-        <v>170</v>
-      </c>
-      <c r="I28" s="14">
-        <v>40</v>
-      </c>
-      <c r="J28" s="14">
-        <v>24</v>
-      </c>
       <c r="K28" s="15">
-        <v>66.666666666666</v>
+        <v>51.851851851851</v>
       </c>
       <c r="L28" s="15">
-        <v>166.666666666667</v>
+        <v>115.789473684211</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>16.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-56.25</v>
       </c>
       <c r="M29" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.666666666666</v>
+        <v>-77.419354838709</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>25</v>
       </c>
       <c r="L30" s="15">
-        <v>-28.571428571428</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-80.769230769230</v>
+        <v>-81.481481481481</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -885,30 +885,30 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>11</v>
@@ -920,13 +920,13 @@
         <v>37.5</v>
       </c>
       <c r="L15" s="15">
-        <v>57.142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="M15" s="15">
         <v>83.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-15.384615384615</v>
+        <v>-21.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>28.571428571428</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>40.740740740740</v>
+        <v>28</v>
       </c>
       <c r="I16" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J16" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.816901408450</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.368421052631</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="M16" s="15">
-        <v>-4.166666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.575757575757</v>
+        <v>-82.142857142857</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15">
-        <v>-10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F17" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G17" s="14">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H17" s="15">
-        <v>11.764705882352</v>
+        <v>7.936507936507</v>
       </c>
       <c r="I17" s="14">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="J17" s="14">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.933774834437</v>
+        <v>-7.514450867052</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.086956521739</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="M17" s="15">
-        <v>46.236559139784</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.299516908212</v>
+        <v>-29.203539823008</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.555555555555</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>-4.444444444444</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.416666666666</v>
+        <v>-23.728813559322</v>
       </c>
       <c r="M18" s="15">
-        <v>-20.370370370370</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.276807980049</v>
+        <v>-89.655172413793</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G19" s="14">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.949152542372</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J19" s="14">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="K19" s="15">
-        <v>-29.139072847682</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.065359477124</v>
+        <v>-30.357142857142</v>
       </c>
       <c r="M19" s="15">
-        <v>75.409836065573</v>
+        <v>80</v>
       </c>
       <c r="N19" s="15">
-        <v>-10.833333333333</v>
+        <v>-11.363636363636</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
         <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>-54.838709677419</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="I20" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J20" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K20" s="15">
-        <v>-45.762711864406</v>
+        <v>-40.625</v>
       </c>
       <c r="L20" s="15">
-        <v>-31.914893617021</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="M20" s="15">
-        <v>33.333333333333</v>
+        <v>26.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.644012944983</v>
+        <v>-88.449848024316</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.388059701492</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="17">
         <v>179</v>
       </c>
       <c r="G21" s="17">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.789473684210</v>
+        <v>-16.744186046511</v>
       </c>
       <c r="I21" s="17">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="J21" s="17">
-        <v>488</v>
+        <v>548</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.032786885245</v>
+        <v>-18.248175182481</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.650557620817</v>
+        <v>-25.827814569536</v>
       </c>
       <c r="M21" s="18">
-        <v>27.795527156549</v>
+        <v>30.612244897959</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.546328071379</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
         <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L22" s="15">
-        <v>-68.421052631578</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
         <v>10</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.076923076923</v>
+        <v>-37.5</v>
       </c>
       <c r="M23" s="15">
         <v>-9.090909090909</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>-35.714285714285</v>
+        <v>19.444444444444</v>
       </c>
       <c r="F24" s="14">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G24" s="14">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.34375</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="I24" s="14">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="J24" s="14">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.329113924050</v>
+        <v>-26.136363636363</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.822349570200</v>
+        <v>-32.467532467532</v>
       </c>
       <c r="M24" s="15">
-        <v>-3.555555555555</v>
+        <v>6.557377049180</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
         <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-63.157894736842</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H25" s="15">
-        <v>-51.020408163265</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="I25" s="14">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="J25" s="14">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.173913043478</v>
+        <v>-45.522388059701</v>
       </c>
       <c r="L25" s="15">
-        <v>-70.430107526881</v>
+        <v>-63.681592039801</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D26" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>-43.478260869565</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F26" s="14">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G26" s="14">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.265306122449</v>
+        <v>-13</v>
       </c>
       <c r="I26" s="14">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="J26" s="14">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.213270142180</v>
+        <v>-7.594936708860</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.419913419913</v>
+        <v>-14.785992217898</v>
       </c>
       <c r="M26" s="15">
-        <v>16.959064327485</v>
+        <v>11.167512690355</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="14">
-        <v>6</v>
-      </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
@@ -1412,7 +1412,7 @@
         <v>-13.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="F28" s="14">
+        <v>17</v>
+      </c>
+      <c r="G28" s="14">
         <v>10</v>
       </c>
-      <c r="G28" s="14">
-        <v>11</v>
-      </c>
       <c r="H28" s="15">
-        <v>-9.090909090909</v>
+        <v>70</v>
       </c>
       <c r="I28" s="14">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J28" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K28" s="15">
-        <v>51.851851851851</v>
+        <v>73.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>115.789473684211</v>
+        <v>126.086956521739</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
@@ -1494,13 +1494,13 @@
         <v>16.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-56.25</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.419354838709</v>
+        <v>-78.787878787878</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1535,13 +1535,13 @@
         <v>25</v>
       </c>
       <c r="L30" s="15">
-        <v>-44.444444444444</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M30" s="15">
         <v>-16.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.481481481481</v>
+        <v>-82.758620689655</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -882,10 +882,10 @@
         <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-21.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15">
-        <v>28</v>
+        <v>23.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="J16" s="14">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.846153846153</v>
+        <v>-2.222222222222</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.470588235294</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.25</v>
+        <v>-2.222222222222</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.142857142857</v>
+        <v>-80.487804878048</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G17" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H17" s="15">
-        <v>7.936507936507</v>
+        <v>2.857142857142</v>
       </c>
       <c r="I17" s="14">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="J17" s="14">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.514450867052</v>
+        <v>-7.329842931937</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.528301886792</v>
+        <v>-22.368421052631</v>
       </c>
       <c r="M17" s="15">
-        <v>53.846153846153</v>
+        <v>51.282051282051</v>
       </c>
       <c r="N17" s="15">
-        <v>-29.203539823008</v>
+        <v>-28.340080971659</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>75</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.809523809523</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.764705882352</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.728813559322</v>
+        <v>-18.75</v>
       </c>
       <c r="M18" s="15">
-        <v>-18.181818181818</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.655172413793</v>
+        <v>-88.865096359743</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F19" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H19" s="15">
-        <v>-41.666666666666</v>
+        <v>-28.985507246376</v>
       </c>
       <c r="I19" s="14">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="K19" s="15">
-        <v>-31.578947368421</v>
+        <v>-26.630434782608</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.357142857142</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="M19" s="15">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N19" s="15">
-        <v>-11.363636363636</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14">
         <v>6</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
       <c r="E20" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-38.709677419354</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J20" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K20" s="15">
-        <v>-40.625</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.490196078431</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>26.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.449848024316</v>
+        <v>-87.465181058495</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D21" s="17">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>-20</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="G21" s="17">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.744186046511</v>
+        <v>-10.407239819004</v>
       </c>
       <c r="I21" s="17">
-        <v>448</v>
+        <v>511</v>
       </c>
       <c r="J21" s="17">
-        <v>548</v>
+        <v>602</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.248175182481</v>
+        <v>-15.116279069767</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.827814569536</v>
+        <v>-23.388305847076</v>
       </c>
       <c r="M21" s="18">
-        <v>30.612244897959</v>
+        <v>34.120734908136</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.428571428571</v>
+        <v>-69.941176470588</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
         <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>-22.222222222222</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>-63.157894736842</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="M22" s="15">
-        <v>75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,28 +1230,28 @@
         <v>-100</v>
       </c>
       <c r="F23" s="14">
+        <v>2</v>
+      </c>
+      <c r="G23" s="14">
         <v>3</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>10</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L23" s="15">
-        <v>-37.5</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="M23" s="15">
-        <v>-9.090909090909</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>29</v>
+      </c>
+      <c r="D24" s="14">
         <v>43</v>
       </c>
-      <c r="D24" s="14">
-        <v>36</v>
-      </c>
       <c r="E24" s="15">
-        <v>19.444444444444</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="F24" s="14">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G24" s="14">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.176470588235</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="I24" s="14">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="J24" s="14">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.136363636363</v>
+        <v>-26.329113924050</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.467532467532</v>
+        <v>-33.561643835616</v>
       </c>
       <c r="M24" s="15">
-        <v>6.557377049180</v>
+        <v>9.398496240601</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G25" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.105263157894</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="I25" s="14">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J25" s="14">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K25" s="15">
-        <v>-45.522388059701</v>
+        <v>-41.496598639455</v>
       </c>
       <c r="L25" s="15">
-        <v>-63.681592039801</v>
+        <v>-63.404255319148</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>-23.076923076923</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="F26" s="14">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G26" s="14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H26" s="15">
-        <v>-13</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="I26" s="14">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="J26" s="14">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.594936708860</v>
+        <v>-10.227272727272</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.785992217898</v>
+        <v>-14.748201438848</v>
       </c>
       <c r="M26" s="15">
-        <v>11.167512690355</v>
+        <v>9.722222222222</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>-7.142857142857</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>266.666666666667</v>
+        <v>-40</v>
       </c>
       <c r="F28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H28" s="15">
-        <v>70</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I28" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J28" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K28" s="15">
-        <v>73.333333333333</v>
+        <v>60</v>
       </c>
       <c r="L28" s="15">
-        <v>126.086956521739</v>
+        <v>107.407407407407</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
@@ -1494,13 +1494,13 @@
         <v>16.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-61.111111111111</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.787878787878</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1535,13 +1535,13 @@
         <v>25</v>
       </c>
       <c r="L30" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-82.758620689655</v>
+        <v>-85.294117647058</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,407 +854,407 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="G14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
         <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.315789473684</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>23.333333333333</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I16" s="14">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J16" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.222222222222</v>
+        <v>-2.105263157894</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.137931034482</v>
+        <v>-26.771653543307</v>
       </c>
       <c r="M16" s="15">
-        <v>-2.222222222222</v>
+        <v>-5.102040816326</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.487804878048</v>
+        <v>-81.059063136456</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="14">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>15</v>
-      </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="G17" s="14">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H17" s="15">
-        <v>2.857142857142</v>
+        <v>2.469135802469</v>
       </c>
       <c r="I17" s="14">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="J17" s="14">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.329842931937</v>
+        <v>-5.188679245283</v>
       </c>
       <c r="L17" s="15">
-        <v>-22.368421052631</v>
+        <v>-17.283950617283</v>
       </c>
       <c r="M17" s="15">
-        <v>51.282051282051</v>
+        <v>60.8</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.340080971659</v>
+        <v>-25.555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
+        <v>19</v>
+      </c>
+      <c r="G18" s="14">
         <v>17</v>
       </c>
-      <c r="G18" s="14">
-        <v>18</v>
-      </c>
       <c r="H18" s="15">
-        <v>-5.555555555555</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.454545454545</v>
+        <v>-5</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.75</v>
+        <v>-25.974025974026</v>
       </c>
       <c r="M18" s="15">
-        <v>-8.771929824561</v>
+        <v>-10.9375</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.865096359743</v>
+        <v>-88.757396449704</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>30.769230769230</v>
+        <v>122.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>-28.985507246376</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="I19" s="14">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="J19" s="14">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="K19" s="15">
-        <v>-26.630434782608</v>
+        <v>-19.689119170984</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.419354838709</v>
+        <v>-23.267326732673</v>
       </c>
       <c r="M19" s="15">
-        <v>87.5</v>
+        <v>103.947368421053</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.25</v>
+        <v>-2.515723270440</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G20" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-6.25</v>
       </c>
       <c r="I20" s="14">
+        <v>58</v>
+      </c>
+      <c r="J20" s="14">
+        <v>79</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-26.582278481012</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-10.769230769230</v>
+      </c>
+      <c r="M20" s="15">
         <v>45</v>
       </c>
-      <c r="J20" s="14">
-        <v>70</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-25</v>
-      </c>
-      <c r="M20" s="15">
-        <v>28.571428571428</v>
-      </c>
       <c r="N20" s="15">
-        <v>-87.465181058495</v>
+        <v>-85.166240409207</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>11.111111111111</v>
+        <v>35.294117647058</v>
       </c>
       <c r="F21" s="17">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="G21" s="17">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.407239819004</v>
+        <v>0.431034482758</v>
       </c>
       <c r="I21" s="17">
-        <v>511</v>
+        <v>580</v>
       </c>
       <c r="J21" s="17">
-        <v>602</v>
+        <v>653</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.116279069767</v>
+        <v>-11.179173047473</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.388305847076</v>
+        <v>-20.329670329670</v>
       </c>
       <c r="M21" s="18">
-        <v>34.120734908136</v>
+        <v>39.759036144578</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.941176470588</v>
+        <v>-68.682505399568</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="14">
+        <v>28</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
         <v>-57.894736842105</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="E23" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
         <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-47.368421052631</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M23" s="15">
-        <v>-28.571428571428</v>
+        <v>-31.25</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D24" s="14">
         <v>43</v>
       </c>
       <c r="E24" s="15">
-        <v>-32.558139534883</v>
+        <v>6.976744186046</v>
       </c>
       <c r="F24" s="14">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="G24" s="14">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.684210526315</v>
+        <v>-9.146341463414</v>
       </c>
       <c r="I24" s="14">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="J24" s="14">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.329113924050</v>
+        <v>-22.602739726027</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.561643835616</v>
+        <v>-28.329809725158</v>
       </c>
       <c r="M24" s="15">
-        <v>9.398496240601</v>
+        <v>16.095890410958</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.461538461538</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F25" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G25" s="14">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.034482758620</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J25" s="14">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="K25" s="15">
-        <v>-41.496598639455</v>
+        <v>-40.963855421686</v>
       </c>
       <c r="L25" s="15">
-        <v>-63.404255319148</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-29.629629629629</v>
+        <v>216.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G26" s="14">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H26" s="15">
-        <v>-26.530612244898</v>
+        <v>1.136363636363</v>
       </c>
       <c r="I26" s="14">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="J26" s="14">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.227272727272</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.748201438848</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="M26" s="15">
-        <v>9.722222222222</v>
+        <v>15</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-12.5</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L27" s="15">
-        <v>-17.647058823529</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>18</v>
@@ -1444,104 +1444,104 @@
         <v>38.461538461538</v>
       </c>
       <c r="I28" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J28" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K28" s="15">
-        <v>60</v>
+        <v>56.756756756756</v>
       </c>
       <c r="L28" s="15">
-        <v>107.407407407407</v>
+        <v>107.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
+        <v>8</v>
+      </c>
+      <c r="J29" s="14">
         <v>7</v>
       </c>
-      <c r="J29" s="14">
-        <v>6</v>
-      </c>
       <c r="K29" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L29" s="15">
-        <v>-63.157894736842</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="M29" s="15">
-        <v>-12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N29" s="15">
-        <v>-81.578947368421</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
+        <v>6</v>
+      </c>
+      <c r="J30" s="14">
+        <v>5</v>
+      </c>
+      <c r="K30" s="15">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="14">
-        <v>5</v>
-      </c>
-      <c r="J30" s="14">
-        <v>4</v>
-      </c>
-      <c r="K30" s="15">
-        <v>25</v>
-      </c>
       <c r="L30" s="15">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.294117647058</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>90</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2187</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1640</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>2299</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>766</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>1744</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>8815</v>

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -882,7 +882,7 @@
         <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N14" s="15">
         <v>-86.666666666666</v>
@@ -890,139 +890,139 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>5</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L15" s="15">
-        <v>40</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-26.315789473684</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
+        <v>22.222222222222</v>
+      </c>
+      <c r="F16" s="14">
+        <v>34</v>
+      </c>
+      <c r="G16" s="14">
+        <v>33</v>
+      </c>
+      <c r="H16" s="15">
+        <v>3.030303030303</v>
+      </c>
+      <c r="I16" s="14">
+        <v>104</v>
+      </c>
+      <c r="J16" s="14">
+        <v>104</v>
+      </c>
+      <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>33</v>
-      </c>
-      <c r="G16" s="14">
-        <v>31</v>
-      </c>
-      <c r="H16" s="15">
-        <v>6.451612903225</v>
-      </c>
-      <c r="I16" s="14">
-        <v>93</v>
-      </c>
-      <c r="J16" s="14">
-        <v>95</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-2.105263157894</v>
-      </c>
       <c r="L16" s="15">
-        <v>-26.771653543307</v>
+        <v>-24.637681159420</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.102040816326</v>
+        <v>2.970297029702</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.059063136456</v>
+        <v>-80.560747663551</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>21</v>
+      </c>
+      <c r="D17" s="14">
         <v>24</v>
       </c>
-      <c r="D17" s="14">
-        <v>21</v>
-      </c>
       <c r="E17" s="15">
-        <v>14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G17" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H17" s="15">
-        <v>2.469135802469</v>
+        <v>2.352941176470</v>
       </c>
       <c r="I17" s="14">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="J17" s="14">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.188679245283</v>
+        <v>-5.932203389830</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.283950617283</v>
+        <v>-15.589353612167</v>
       </c>
       <c r="M17" s="15">
-        <v>60.8</v>
+        <v>58.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>-25.555555555555</v>
+        <v>-24.489795918367</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
         <v>19</v>
@@ -1034,186 +1034,186 @@
         <v>11.764705882352</v>
       </c>
       <c r="I18" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J18" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K18" s="15">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.974025974026</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.9375</v>
+        <v>-4.615384615384</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.757396449704</v>
+        <v>-88.539741219963</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>122.222222222222</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="14">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.030303030303</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="J19" s="14">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.689119170984</v>
+        <v>-22.596153846153</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.267326732673</v>
+        <v>-24.056603773584</v>
       </c>
       <c r="M19" s="15">
-        <v>103.947368421053</v>
+        <v>103.79746835443</v>
       </c>
       <c r="N19" s="15">
-        <v>-2.515723270440</v>
+        <v>-6.936416184971</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
         <v>30</v>
       </c>
       <c r="G20" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>-6.25</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J20" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.582278481012</v>
+        <v>-27.058823529411</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.769230769230</v>
+        <v>-15.068493150684</v>
       </c>
       <c r="M20" s="15">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.166240409207</v>
+        <v>-85.096153846153</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18">
-        <v>35.294117647058</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G21" s="17">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="H21" s="18">
-        <v>0.431034482758</v>
+        <v>3.619909502262</v>
       </c>
       <c r="I21" s="17">
-        <v>580</v>
+        <v>629</v>
       </c>
       <c r="J21" s="17">
-        <v>653</v>
+        <v>709</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.179173047473</v>
+        <v>-11.283497884344</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.329670329670</v>
+        <v>-19.872611464968</v>
       </c>
       <c r="M21" s="18">
-        <v>39.759036144578</v>
+        <v>43.607305936073</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.682505399568</v>
+        <v>-68.455366098294</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-57.894736842105</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>29</v>
+      <c r="D23" s="14">
+        <v>4</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J23" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>-42.105263157894</v>
+        <v>-40</v>
       </c>
       <c r="M23" s="15">
-        <v>-31.25</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15">
-        <v>6.976744186046</v>
+        <v>-44.680851063829</v>
       </c>
       <c r="F24" s="14">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G24" s="14">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.146341463414</v>
+        <v>-12.426035502958</v>
       </c>
       <c r="I24" s="14">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="J24" s="14">
-        <v>438</v>
+        <v>485</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.602739726027</v>
+        <v>-24.948453608247</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.329809725158</v>
+        <v>-27.920792079207</v>
       </c>
       <c r="M24" s="15">
-        <v>16.095890410958</v>
+        <v>14.826498422712</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-42.105263157894</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G25" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.571428571428</v>
+        <v>-28.767123287671</v>
       </c>
       <c r="I25" s="14">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J25" s="14">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="K25" s="15">
-        <v>-40.963855421686</v>
+        <v>-43.617021276595</v>
       </c>
       <c r="L25" s="15">
-        <v>-61.111111111111</v>
+        <v>-60.885608856088</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>216.666666666667</v>
+        <v>29.411764705882</v>
       </c>
       <c r="F26" s="14">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G26" s="14">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H26" s="15">
-        <v>1.136363636363</v>
+        <v>19.512195121951</v>
       </c>
       <c r="I26" s="14">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="J26" s="14">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>1.706484641638</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.122448979591</v>
+        <v>-5.396825396825</v>
       </c>
       <c r="M26" s="15">
-        <v>15</v>
+        <v>17.322834645669</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
         <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-5.882352941176</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L27" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G28" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>38.461538461538</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I28" s="14">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J28" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K28" s="15">
-        <v>56.756756756756</v>
+        <v>55.263157894736</v>
       </c>
       <c r="L28" s="15">
-        <v>107.142857142857</v>
+        <v>90.322580645161</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L29" s="15">
-        <v>-57.894736842105</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M29" s="15">
-        <v>-11.111111111111</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-78.048780487804</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="14">
         <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-81.081081081081</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>90</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>2187</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1640</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>2299</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>766</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>1744</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>8815</v>

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,10 +873,10 @@
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L14" s="15">
         <v>-50</v>
@@ -885,48 +885,48 @@
         <v>-71.428571428571</v>
       </c>
       <c r="N14" s="15">
-        <v>-86.666666666666</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L15" s="15">
-        <v>23.076923076923</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>142.857142857143</v>
       </c>
       <c r="N15" s="15">
-        <v>-20</v>
+        <v>-22.727272727272</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>22.222222222222</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H16" s="15">
-        <v>3.030303030303</v>
+        <v>3.125</v>
       </c>
       <c r="I16" s="14">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J16" s="14">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K16" s="15">
+        <v>-0.909090909090</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-26.351351351351</v>
+      </c>
+      <c r="M16" s="15">
         <v>0</v>
       </c>
-      <c r="L16" s="15">
-        <v>-24.637681159420</v>
-      </c>
-      <c r="M16" s="15">
-        <v>2.970297029702</v>
-      </c>
       <c r="N16" s="15">
-        <v>-80.560747663551</v>
+        <v>-80.977312390925</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.5</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F17" s="14">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G17" s="14">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H17" s="15">
-        <v>2.352941176470</v>
+        <v>-2.469135802469</v>
       </c>
       <c r="I17" s="14">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="J17" s="14">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.932203389830</v>
+        <v>-5.511811023622</v>
       </c>
       <c r="L17" s="15">
-        <v>-15.589353612167</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="M17" s="15">
-        <v>58.571428571428</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.489795918367</v>
+        <v>-22.580645161290</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G18" s="14">
         <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>11.764705882352</v>
+        <v>35.294117647058</v>
       </c>
       <c r="I18" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J18" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K18" s="15">
         <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.390243902439</v>
+        <v>-21.839080459770</v>
       </c>
       <c r="M18" s="15">
-        <v>-4.615384615384</v>
+        <v>-4.225352112676</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.539741219963</v>
+        <v>-88.296041308089</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
         <v>6</v>
       </c>
-      <c r="D19" s="14">
-        <v>15</v>
-      </c>
       <c r="E19" s="15">
-        <v>-60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.263157894736</v>
+        <v>23.255813953488</v>
       </c>
       <c r="I19" s="14">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="J19" s="14">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.596153846153</v>
+        <v>-20.093457943925</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.056603773584</v>
+        <v>-25.974025974026</v>
       </c>
       <c r="M19" s="15">
-        <v>103.79746835443</v>
+        <v>92.134831460674</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.936416184971</v>
+        <v>-8.064516129032</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
         <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>15.384615384615</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I20" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J20" s="14">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K20" s="15">
-        <v>-27.058823529411</v>
+        <v>-24.175824175824</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.068493150684</v>
+        <v>-13.75</v>
       </c>
       <c r="M20" s="15">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.096153846153</v>
+        <v>-84.632516703786</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>9.302325581395</v>
       </c>
       <c r="F21" s="17">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G21" s="17">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="H21" s="18">
-        <v>3.619909502262</v>
+        <v>10.784313725490</v>
       </c>
       <c r="I21" s="17">
-        <v>629</v>
+        <v>676</v>
       </c>
       <c r="J21" s="17">
-        <v>709</v>
+        <v>752</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.283497884344</v>
+        <v>-10.106382978723</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.872611464968</v>
+        <v>-20.094562647754</v>
       </c>
       <c r="M21" s="18">
-        <v>43.607305936073</v>
+        <v>39.381443298969</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.455366098294</v>
+        <v>-68.411214953271</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L22" s="15">
         <v>-50</v>
       </c>
       <c r="M22" s="15">
-        <v>42.857142857142</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-18.75</v>
       </c>
       <c r="L23" s="15">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="M23" s="15">
-        <v>-29.411764705882</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E24" s="15">
-        <v>-44.680851063829</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="F24" s="14">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="G24" s="14">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.426035502958</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I24" s="14">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="J24" s="14">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.948453608247</v>
+        <v>-25</v>
       </c>
       <c r="L24" s="15">
-        <v>-27.920792079207</v>
+        <v>-28.044280442804</v>
       </c>
       <c r="M24" s="15">
-        <v>14.826498422712</v>
+        <v>16.071428571428</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-63.636363636363</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.767123287671</v>
+        <v>-39.344262295082</v>
       </c>
       <c r="I25" s="14">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="J25" s="14">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.617021276595</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="L25" s="15">
-        <v>-60.885608856088</v>
+        <v>-60.616438356164</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>29.411764705882</v>
+        <v>-4</v>
       </c>
       <c r="F26" s="14">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G26" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" s="15">
-        <v>19.512195121951</v>
+        <v>27.160493827160</v>
       </c>
       <c r="I26" s="14">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="J26" s="14">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="K26" s="15">
-        <v>1.706484641638</v>
+        <v>0.943396226415</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.396825396825</v>
+        <v>-7.492795389048</v>
       </c>
       <c r="M26" s="15">
-        <v>17.322834645669</v>
+        <v>13.427561837455</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
         <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>5.882352941176</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,54 +1426,54 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>54.545454545454</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J28" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K28" s="15">
-        <v>55.263157894736</v>
+        <v>51.219512195122</v>
       </c>
       <c r="L28" s="15">
-        <v>90.322580645161</v>
+        <v>72.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1494,27 +1494,27 @@
         <v>28.571428571428</v>
       </c>
       <c r="L29" s="15">
-        <v>-52.631578947368</v>
+        <v>-55</v>
       </c>
       <c r="M29" s="15">
         <v>-18.181818181818</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.048780487804</v>
+        <v>-79.545454545454</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
@@ -1535,13 +1535,13 @@
         <v>40</v>
       </c>
       <c r="L30" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M30" s="15">
         <v>-30</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.081081081081</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>90</v>

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -879,10 +879,10 @@
         <v>-60</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M14" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
         <v>-89.473684210526</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>70</v>
+        <v>81.818181818181</v>
       </c>
       <c r="L15" s="15">
-        <v>21.428571428571</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>142.857142857143</v>
+        <v>185.714285714286</v>
       </c>
       <c r="N15" s="15">
-        <v>-22.727272727272</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>-56.25</v>
       </c>
       <c r="F16" s="14">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15">
-        <v>3.125</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J16" s="14">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K16" s="15">
-        <v>-0.909090909090</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.351351351351</v>
+        <v>-28.395061728395</v>
       </c>
       <c r="M16" s="15">
-        <v>0</v>
+        <v>-2.521008403361</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.977312390925</v>
+        <v>-80.983606557377</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D17" s="14">
         <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>-5.555555555555</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F17" s="14">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G17" s="14">
         <v>81</v>
       </c>
       <c r="H17" s="15">
-        <v>-2.469135802469</v>
+        <v>8.641975308641</v>
       </c>
       <c r="I17" s="14">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="J17" s="14">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.511811023622</v>
+        <v>-2.205882352941</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.893617021276</v>
+        <v>-12.5</v>
       </c>
       <c r="M17" s="15">
-        <v>53.846153846153</v>
+        <v>64.197530864197</v>
       </c>
       <c r="N17" s="15">
-        <v>-22.580645161290</v>
+        <v>-18.404907975460</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="F18" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>35.294117647058</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I18" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J18" s="14">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-6.578947368421</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.839080459770</v>
+        <v>-21.978021978022</v>
       </c>
       <c r="M18" s="15">
-        <v>-4.225352112676</v>
+        <v>-4.054054054054</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.296041308089</v>
+        <v>-88.474025974026</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>66.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H19" s="15">
-        <v>23.255813953488</v>
+        <v>21.621621621621</v>
       </c>
       <c r="I19" s="14">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J19" s="14">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.093457943925</v>
+        <v>-18.552036199095</v>
       </c>
       <c r="L19" s="15">
-        <v>-25.974025974026</v>
+        <v>-28.286852589641</v>
       </c>
       <c r="M19" s="15">
-        <v>92.134831460674</v>
+        <v>87.5</v>
       </c>
       <c r="N19" s="15">
-        <v>-8.064516129032</v>
+        <v>-9.090909090909</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>18.518518518518</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>69</v>
       </c>
       <c r="J20" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K20" s="15">
-        <v>-24.175824175824</v>
+        <v>-26.595744680851</v>
       </c>
       <c r="L20" s="15">
-        <v>-13.75</v>
+        <v>-27.368421052631</v>
       </c>
       <c r="M20" s="15">
-        <v>50</v>
+        <v>40.816326530612</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.632516703786</v>
+        <v>-85.504201680672</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" s="17">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>9.302325581395</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="F21" s="17">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="G21" s="17">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H21" s="18">
-        <v>10.784313725490</v>
+        <v>4.433497536945</v>
       </c>
       <c r="I21" s="17">
-        <v>676</v>
+        <v>724</v>
       </c>
       <c r="J21" s="17">
-        <v>752</v>
+        <v>805</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.106382978723</v>
+        <v>-10.062111801242</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.094562647754</v>
+        <v>-21.560130010834</v>
       </c>
       <c r="M21" s="18">
-        <v>39.381443298969</v>
+        <v>40.582524271844</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.411214953271</v>
+        <v>-68.105726872246</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,37 +1183,37 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>-28.571428571428</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="M22" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1230,31 +1230,31 @@
         <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.75</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L23" s="15">
-        <v>-35</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M23" s="15">
-        <v>-31.578947368421</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.428571428571</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="F24" s="14">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G24" s="14">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.809523809523</v>
+        <v>-22.754491017964</v>
       </c>
       <c r="I24" s="14">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="J24" s="14">
-        <v>520</v>
+        <v>562</v>
       </c>
       <c r="K24" s="15">
-        <v>-25</v>
+        <v>-24.911032028469</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.044280442804</v>
+        <v>-27.491408934707</v>
       </c>
       <c r="M24" s="15">
-        <v>16.071428571428</v>
+        <v>14.986376021798</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>28.571428571428</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F25" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" s="14">
         <v>61</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.344262295082</v>
+        <v>-37.704918032786</v>
       </c>
       <c r="I25" s="14">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J25" s="14">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="K25" s="15">
-        <v>-41.025641025641</v>
+        <v>-39.903846153846</v>
       </c>
       <c r="L25" s="15">
-        <v>-60.616438356164</v>
+        <v>-59.807073954983</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-4</v>
+        <v>61.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G26" s="14">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H26" s="15">
-        <v>27.160493827160</v>
+        <v>54.166666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="J26" s="14">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="K26" s="15">
-        <v>0.943396226415</v>
+        <v>3.273809523809</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.492795389048</v>
+        <v>-3.878116343490</v>
       </c>
       <c r="M26" s="15">
-        <v>13.427561837455</v>
+        <v>10.509554140127</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>300</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="I27" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27" s="15">
-        <v>17.647058823529</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-13.043478260869</v>
+        <v>-4</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,120 +1428,120 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-33.333333333333</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J28" s="14">
         <v>41</v>
       </c>
       <c r="K28" s="15">
-        <v>51.219512195122</v>
+        <v>56.097560975609</v>
       </c>
       <c r="L28" s="15">
-        <v>72.222222222222</v>
+        <v>68.421052631578</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L29" s="15">
-        <v>-55</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N29" s="15">
-        <v>-79.545454545454</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="14">
         <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L30" s="15">
-        <v>-46.153846153846</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.578947368421</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>90</v>

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -879,13 +879,13 @@
         <v>-60</v>
       </c>
       <c r="L14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-89.473684210526</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,13 +893,13 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
         <v>8</v>
@@ -911,22 +911,22 @@
         <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>81.818181818181</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="M15" s="15">
-        <v>185.714285714286</v>
+        <v>175</v>
       </c>
       <c r="N15" s="15">
-        <v>-20</v>
+        <v>-18.518518518518</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-56.25</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.222222222222</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="I16" s="14">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J16" s="14">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.936507936507</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.395061728395</v>
+        <v>-30.285714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>-2.521008403361</v>
+        <v>-3.937007874015</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.983606557377</v>
+        <v>-80.967238689547</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E17" s="15">
-        <v>22.222222222222</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F17" s="14">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G17" s="14">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H17" s="15">
-        <v>8.641975308641</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="J17" s="14">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.205882352941</v>
+        <v>-2.990033222591</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.5</v>
+        <v>-9.316770186335</v>
       </c>
       <c r="M17" s="15">
-        <v>64.197530864197</v>
+        <v>71.764705882352</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.404907975460</v>
+        <v>-15.606936416185</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-9.523809523809</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J18" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K18" s="15">
-        <v>-6.578947368421</v>
+        <v>-3.658536585365</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.978021978022</v>
+        <v>-18.556701030927</v>
       </c>
       <c r="M18" s="15">
-        <v>-4.054054054054</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.474025974026</v>
+        <v>-88.012139605462</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>28.571428571428</v>
+        <v>63.636363636363</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>21.621621621621</v>
+        <v>10.256410256410</v>
       </c>
       <c r="I19" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="J19" s="14">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.552036199095</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.286852589641</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="M19" s="15">
-        <v>87.5</v>
+        <v>81.818181818181</v>
       </c>
       <c r="N19" s="15">
-        <v>-9.090909090909</v>
+        <v>-6.542056074766</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I20" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J20" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.595744680851</v>
+        <v>-24</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.368421052631</v>
+        <v>-26.213592233009</v>
       </c>
       <c r="M20" s="15">
-        <v>40.816326530612</v>
+        <v>43.396226415094</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.504201680672</v>
+        <v>-84.890656063618</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.207547169811</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G21" s="17">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H21" s="18">
-        <v>4.433497536945</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="I21" s="17">
-        <v>724</v>
+        <v>793</v>
       </c>
       <c r="J21" s="17">
-        <v>805</v>
+        <v>866</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.062111801242</v>
+        <v>-8.429561200923</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.560130010834</v>
+        <v>-19.410569105691</v>
       </c>
       <c r="M21" s="18">
-        <v>40.582524271844</v>
+        <v>42.882882882882</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.105726872246</v>
+        <v>-67.095435684647</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
         <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>-41.176470588235</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L22" s="15">
-        <v>-52.380952380952</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M22" s="15">
-        <v>-9.090909090909</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
+        <v>200</v>
+      </c>
+      <c r="F23" s="14">
+        <v>6</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="I23" s="14">
+        <v>18</v>
+      </c>
+      <c r="J23" s="14">
+        <v>18</v>
+      </c>
+      <c r="K23" s="15">
         <v>0</v>
       </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="14">
-        <v>6</v>
-      </c>
-      <c r="H23" s="15">
+      <c r="L23" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="I23" s="14">
-        <v>14</v>
-      </c>
-      <c r="J23" s="14">
-        <v>17</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-17.647058823529</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-36.363636363636</v>
-      </c>
       <c r="M23" s="15">
-        <v>-26.315789473684</v>
+        <v>-10</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-26.190476190476</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="F24" s="14">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G24" s="14">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.754491017964</v>
+        <v>-27.950310559006</v>
       </c>
       <c r="I24" s="14">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="J24" s="14">
-        <v>562</v>
+        <v>599</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.911032028469</v>
+        <v>-24.207011686143</v>
       </c>
       <c r="L24" s="15">
-        <v>-27.491408934707</v>
+        <v>-28.050713153724</v>
       </c>
       <c r="M24" s="15">
-        <v>14.986376021798</v>
+        <v>16.112531969309</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.076923076923</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F25" s="14">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.704918032786</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="J25" s="14">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="K25" s="15">
-        <v>-39.903846153846</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="L25" s="15">
-        <v>-59.807073954983</v>
+        <v>-57.647058823529</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>61.111111111111</v>
+        <v>110</v>
       </c>
       <c r="F26" s="14">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G26" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H26" s="15">
-        <v>54.166666666666</v>
+        <v>40</v>
       </c>
       <c r="I26" s="14">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="J26" s="14">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="K26" s="15">
-        <v>3.273809523809</v>
+        <v>8.146067415730</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.878116343490</v>
+        <v>-1.282051282051</v>
       </c>
       <c r="M26" s="15">
-        <v>10.509554140127</v>
+        <v>15.269461077844</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>9</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="L27" s="15">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>400</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J28" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K28" s="15">
-        <v>56.097560975609</v>
+        <v>64.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>68.421052631578</v>
+        <v>76.923076923076</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-50</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>42.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-56</v>
       </c>
       <c r="M29" s="15">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.260869565217</v>
+        <v>-77.551020408163</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
@@ -1526,22 +1526,22 @@
         <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-46.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -879,54 +879,54 @@
         <v>-60</v>
       </c>
       <c r="L14" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M14" s="15">
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-90</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>83.333333333333</v>
+        <v>76.923076923076</v>
       </c>
       <c r="L15" s="15">
-        <v>37.5</v>
+        <v>27.777777777777</v>
       </c>
       <c r="M15" s="15">
-        <v>175</v>
+        <v>187.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-18.518518518518</v>
+        <v>-17.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="F16" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H16" s="15">
-        <v>-25.641025641025</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="I16" s="14">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J16" s="14">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.955223880597</v>
+        <v>-15.032679738562</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.285714285714</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M16" s="15">
-        <v>-3.937007874015</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.967238689547</v>
+        <v>-80.568011958146</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15">
-        <v>-20.689655172413</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F17" s="14">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G17" s="14">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>4.597701149425</v>
       </c>
       <c r="I17" s="14">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="J17" s="14">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.990033222591</v>
+        <v>-1.547987616099</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.316770186335</v>
+        <v>-6.194690265486</v>
       </c>
       <c r="M17" s="15">
-        <v>71.764705882352</v>
+        <v>77.653631284916</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.606936416185</v>
+        <v>-15.873015873015</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,10 +1016,10 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
         <v>0</v>
@@ -1028,28 +1028,28 @@
         <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-4.545454545454</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J18" s="14">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K18" s="15">
-        <v>-3.658536585365</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.556701030927</v>
+        <v>-16</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>1.204819277108</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.012139605462</v>
+        <v>-87.772925764192</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>17</v>
+      </c>
+      <c r="D19" s="14">
         <v>18</v>
       </c>
-      <c r="D19" s="14">
-        <v>11</v>
-      </c>
       <c r="E19" s="15">
-        <v>63.636363636363</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>10.256410256410</v>
+        <v>26.190476190476</v>
       </c>
       <c r="I19" s="14">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="J19" s="14">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.793103448275</v>
+        <v>-13.6</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.528301886792</v>
+        <v>-24.210526315789</v>
       </c>
       <c r="M19" s="15">
-        <v>81.818181818181</v>
+        <v>78.512396694214</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.542056074766</v>
+        <v>-6.493506493506</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H20" s="15">
-        <v>-19.047619047619</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="I20" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J20" s="14">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="K20" s="15">
-        <v>-24</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.213592233009</v>
+        <v>-24.299065420560</v>
       </c>
       <c r="M20" s="15">
-        <v>43.396226415094</v>
+        <v>47.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.890656063618</v>
+        <v>-84.831460674157</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="F21" s="17">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="G21" s="17">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.816901408450</v>
+        <v>-8.085106382978</v>
       </c>
       <c r="I21" s="17">
-        <v>793</v>
+        <v>854</v>
       </c>
       <c r="J21" s="17">
-        <v>866</v>
+        <v>944</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.429561200923</v>
+        <v>-9.533898305084</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.410569105691</v>
+        <v>-17.567567567567</v>
       </c>
       <c r="M21" s="18">
-        <v>42.882882882882</v>
+        <v>43.048576214405</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.095435684647</v>
+        <v>-66.483516483516</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
         <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>-29.411764705882</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L22" s="15">
-        <v>-45.454545454545</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.285714285714</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>-10</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>-2.702702702702</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F24" s="14">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G24" s="14">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.950310559006</v>
+        <v>-12.418300653594</v>
       </c>
       <c r="I24" s="14">
-        <v>454</v>
+        <v>500</v>
       </c>
       <c r="J24" s="14">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.207011686143</v>
+        <v>-21.630094043887</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.050713153724</v>
+        <v>-26.253687315634</v>
       </c>
       <c r="M24" s="15">
-        <v>16.112531969309</v>
+        <v>19.617224880382</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>42.857142857142</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G25" s="14">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I25" s="14">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J25" s="14">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.135135135135</v>
+        <v>-30.901287553648</v>
       </c>
       <c r="L25" s="15">
-        <v>-57.647058823529</v>
+        <v>-55.890410958904</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>110</v>
+        <v>15.789473684210</v>
       </c>
       <c r="F26" s="14">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G26" s="14">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H26" s="15">
-        <v>40</v>
+        <v>35.365853658536</v>
       </c>
       <c r="I26" s="14">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="J26" s="14">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K26" s="15">
-        <v>8.146067415730</v>
+        <v>8</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.282051282051</v>
+        <v>-3.341288782816</v>
       </c>
       <c r="M26" s="15">
-        <v>15.269461077844</v>
+        <v>12.188365650969</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>26</v>
       </c>
       <c r="J27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" s="15">
-        <v>30</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I28" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J28" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K28" s="15">
-        <v>64.285714285714</v>
+        <v>63.043478260869</v>
       </c>
       <c r="L28" s="15">
-        <v>76.923076923076</v>
+        <v>63.043478260869</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,23 +1466,23 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F29" s="14">
-        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>11</v>
@@ -1494,36 +1494,36 @@
         <v>22.222222222222</v>
       </c>
       <c r="L29" s="15">
-        <v>-56</v>
+        <v>-60.714285714285</v>
       </c>
       <c r="M29" s="15">
         <v>-15.384615384615</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.551020408163</v>
+        <v>-79.245283018867</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>9</v>
@@ -1535,13 +1535,13 @@
         <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-78.571428571428</v>
+        <v>-79.545454545454</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-044pct.xlsx
+++ b/data/source/weekly/cs-en-us-044pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -885,7 +885,7 @@
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.476190476190</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>133.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>23</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>76.923076923076</v>
+        <v>53.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>27.777777777777</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M15" s="15">
-        <v>187.5</v>
+        <v>155.555555555556</v>
       </c>
       <c r="N15" s="15">
-        <v>-17.857142857142</v>
+        <v>-23.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.894736842105</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G16" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H16" s="15">
-        <v>-46.938775510204</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="I16" s="14">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="J16" s="14">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.032679738562</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.777777777777</v>
+        <v>-25.906735751295</v>
       </c>
       <c r="M16" s="15">
-        <v>-9.090909090909</v>
+        <v>-5.921052631578</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.568011958146</v>
+        <v>-79.802259887005</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>9.090909090909</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F17" s="14">
         <v>91</v>
       </c>
       <c r="G17" s="14">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H17" s="15">
-        <v>4.597701149425</v>
+        <v>1.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="J17" s="14">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.547987616099</v>
+        <v>-2.034883720930</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.194690265486</v>
+        <v>-8.918918918918</v>
       </c>
       <c r="M17" s="15">
-        <v>77.653631284916</v>
+        <v>75.520833333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.873015873015</v>
+        <v>-16.790123456790</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.5</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I18" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J18" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" s="15">
-        <v>-2.325581395348</v>
+        <v>2.247191011235</v>
       </c>
       <c r="L18" s="15">
-        <v>-16</v>
+        <v>-9.900990099009</v>
       </c>
       <c r="M18" s="15">
-        <v>1.204819277108</v>
+        <v>7.058823529411</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.772925764192</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
         <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H19" s="15">
-        <v>26.190476190476</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="J19" s="14">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.6</v>
+        <v>-15.298507462686</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.210526315789</v>
+        <v>-25.573770491803</v>
       </c>
       <c r="M19" s="15">
-        <v>78.512396694214</v>
+        <v>78.740157480315</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.493506493506</v>
+        <v>-8.835341365461</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>-64.285714285714</v>
+        <v>-70</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H20" s="15">
-        <v>-37.931034482758</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="I20" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J20" s="14">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.947368421052</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.299065420560</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M20" s="15">
-        <v>47.272727272727</v>
+        <v>42.372881355932</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.831460674157</v>
+        <v>-84.782608695652</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E21" s="18">
-        <v>-25.641025641025</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="F21" s="17">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G21" s="17">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.085106382978</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="I21" s="17">
-        <v>854</v>
+        <v>907</v>
       </c>
       <c r="J21" s="17">
-        <v>944</v>
+        <v>1010</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.533898305084</v>
+        <v>-10.198019801980</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.567567567567</v>
+        <v>-18.214607754734</v>
       </c>
       <c r="M21" s="18">
-        <v>43.048576214405</v>
+        <v>43.512658227848</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.483516483516</v>
+        <v>-66.332590942835</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
         <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>-23.529411764705</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L22" s="15">
-        <v>-45.833333333333</v>
+        <v>-48</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I23" s="14">
         <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="15">
         <v>-36.666666666666</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" s="15">
-        <v>15.384615384615</v>
+        <v>-40</v>
       </c>
       <c r="F24" s="14">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G24" s="14">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.418300653594</v>
+        <v>-16.455696202531</v>
       </c>
       <c r="I24" s="14">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="J24" s="14">
-        <v>638</v>
+        <v>678</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.630094043887</v>
+        <v>-22.861356932153</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.253687315634</v>
+        <v>-26.441631504922</v>
       </c>
       <c r="M24" s="15">
-        <v>19.617224880382</v>
+        <v>16.741071428571</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>45.454545454545</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H25" s="15">
-        <v>22.222222222222</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="I25" s="14">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J25" s="14">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.901287553648</v>
+        <v>-33.064516129032</v>
       </c>
       <c r="L25" s="15">
-        <v>-55.890410958904</v>
+        <v>-57.105943152454</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E26" s="15">
-        <v>15.789473684210</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="F26" s="14">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G26" s="14">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>35.365853658536</v>
+        <v>31.395348837209</v>
       </c>
       <c r="I26" s="14">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="J26" s="14">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="K26" s="15">
-        <v>8</v>
+        <v>6.188118811881</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.341288782816</v>
+        <v>-6.331877729257</v>
       </c>
       <c r="M26" s="15">
-        <v>12.188365650969</v>
+        <v>9.438775510204</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>26</v>
       </c>
       <c r="J27" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K27" s="15">
-        <v>23.809523809523</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L27" s="15">
-        <v>-7.142857142857</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>15</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>87.5</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J28" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K28" s="15">
-        <v>63.043478260869</v>
+        <v>60.416666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>63.043478260869</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>22.222222222222</v>
       </c>
       <c r="L29" s="15">
-        <v>-60.714285714285</v>
+        <v>-63.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-15.384615384615</v>
       </c>
       <c r="N29" s="15">
-        <v>-79.245283018867</v>
+        <v>-80.701754385964</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M30" s="15">
         <v>-25</v>
       </c>
       <c r="N30" s="15">
-        <v>-79.545454545454</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-100</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>
